--- a/storage/app/public/vocabs/geologicalsetting/1.3/geologicalsetting_1-3.xlsx
+++ b/storage/app/public/vocabs/geologicalsetting/1.3/geologicalsetting_1-3.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="391">
   <si>
     <t>synonyms</t>
   </si>
@@ -1188,207 +1188,6 @@
   </si>
   <si>
     <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/surface_morphological_setting-marine_setting-abyssal_setting</t>
-  </si>
-  <si>
-    <t>antropogenic setting</t>
-  </si>
-  <si>
-    <t>#human subsurface use</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting</t>
-  </si>
-  <si>
-    <t>gas field</t>
-  </si>
-  <si>
-    <t>#hydrocarbon field#gas reservoir#hydrocarbon reservoir</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-gas_field</t>
-  </si>
-  <si>
-    <t>oil field</t>
-  </si>
-  <si>
-    <t>#oil reservoir#hydrocarbon field#hydrocarbon reservoir</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-oil_field</t>
-  </si>
-  <si>
-    <t>geothermal energy field</t>
-  </si>
-  <si>
-    <t>#geothermal</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-geothermal_energy_field</t>
-  </si>
-  <si>
-    <t>subsurface storage</t>
-  </si>
-  <si>
-    <t>#subsurface disposal#geological storage</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-subsurface_storage</t>
-  </si>
-  <si>
-    <t>gas storage</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-subsurface_storage-gas_storage</t>
-  </si>
-  <si>
-    <t>oil storage</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-subsurface_storage-oil_storage</t>
-  </si>
-  <si>
-    <t>radio-active waste storage</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-subsurface_storage-radio-active_waste_storage</t>
-  </si>
-  <si>
-    <t>CO2 storage</t>
-  </si>
-  <si>
-    <t>#carbon dioxide storage#carbondioxide storage</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-subsurface_storage-co2_storage</t>
-  </si>
-  <si>
-    <t>N2 storage</t>
-  </si>
-  <si>
-    <t>#nitrogen storage</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-subsurface_storage-n2_storage</t>
-  </si>
-  <si>
-    <t>heat storage</t>
-  </si>
-  <si>
-    <t>#geothermal energy storage</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-subsurface_storage-heat_storage</t>
-  </si>
-  <si>
-    <t>brine storage</t>
-  </si>
-  <si>
-    <t>#brackish water storage#salt water storage</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-subsurface_storage-brine_storage</t>
-  </si>
-  <si>
-    <t>waste water storage</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-subsurface_storage-waste_water_storage</t>
-  </si>
-  <si>
-    <t>drinking water storage</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-subsurface_storage-drinking_water_storage</t>
-  </si>
-  <si>
-    <t>ore mine</t>
-  </si>
-  <si>
-    <t>#mineral mine#ore deposit</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-ore_mine</t>
-  </si>
-  <si>
-    <t>mine tailing</t>
-  </si>
-  <si>
-    <t>#mine wastes#mine waste#mine waste disposal#mine disposal</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-ore_mine-mine_tailing</t>
-  </si>
-  <si>
-    <t>civil engineered setting</t>
-  </si>
-  <si>
-    <t>#civil engineering#civil engineered</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-civil_engineered_setting</t>
-  </si>
-  <si>
-    <t>underground research facility</t>
-  </si>
-  <si>
-    <t>#underground science lab</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-civil_engineered_setting-underground_research_facility</t>
-  </si>
-  <si>
-    <t>tunnel</t>
-  </si>
-  <si>
-    <t>#highway tunnel#road tunnel</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-civil_engineered_setting-tunnel</t>
-  </si>
-  <si>
-    <t>dam construction - geological aspects</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-civil_engineered_setting-dam_construction_-_geological_aspects</t>
-  </si>
-  <si>
-    <t>road construction - geotechnical aspects</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-civil_engineered_setting-road_construction_-_geotechnical_aspects</t>
-  </si>
-  <si>
-    <t>building foundation</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-civil_engineered_setting-building_foundation</t>
-  </si>
-  <si>
-    <t>Induced seismicity</t>
-  </si>
-  <si>
-    <t>#induced earthquake#induced seismic</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-induced_seismicity</t>
-  </si>
-  <si>
-    <t>surface subsidence</t>
-  </si>
-  <si>
-    <t>#subsidence</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-surface_subsidence</t>
-  </si>
-  <si>
-    <t>sinkhole</t>
-  </si>
-  <si>
-    <t>#sink hole</t>
-  </si>
-  <si>
-    <t>https://epos-msl.uu.nl/voc/geologicalsetting/1.3/antropogenic_setting-surface_subsidence-sinkhole</t>
   </si>
 </sst>
 </file>
@@ -1728,7 +1527,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3240,257 +3039,6 @@
       </c>
       <c r="F157" t="s">
         <v>390</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8">
-      <c r="A158" t="s">
-        <v>391</v>
-      </c>
-      <c r="E158" t="s">
-        <v>392</v>
-      </c>
-      <c r="F158" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
-      <c r="B159" t="s">
-        <v>394</v>
-      </c>
-      <c r="E159" t="s">
-        <v>395</v>
-      </c>
-      <c r="F159" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8">
-      <c r="B160" t="s">
-        <v>397</v>
-      </c>
-      <c r="E160" t="s">
-        <v>398</v>
-      </c>
-      <c r="F160" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8">
-      <c r="B161" t="s">
-        <v>400</v>
-      </c>
-      <c r="E161" t="s">
-        <v>401</v>
-      </c>
-      <c r="F161" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8">
-      <c r="B162" t="s">
-        <v>403</v>
-      </c>
-      <c r="E162" t="s">
-        <v>404</v>
-      </c>
-      <c r="F162" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8">
-      <c r="C163" t="s">
-        <v>406</v>
-      </c>
-      <c r="F163" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8">
-      <c r="C164" t="s">
-        <v>408</v>
-      </c>
-      <c r="F164" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8">
-      <c r="C165" t="s">
-        <v>410</v>
-      </c>
-      <c r="F165" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8">
-      <c r="C166" t="s">
-        <v>412</v>
-      </c>
-      <c r="E166" t="s">
-        <v>413</v>
-      </c>
-      <c r="F166" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8">
-      <c r="C167" t="s">
-        <v>415</v>
-      </c>
-      <c r="E167" t="s">
-        <v>416</v>
-      </c>
-      <c r="F167" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8">
-      <c r="C168" t="s">
-        <v>418</v>
-      </c>
-      <c r="E168" t="s">
-        <v>419</v>
-      </c>
-      <c r="F168" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8">
-      <c r="C169" t="s">
-        <v>421</v>
-      </c>
-      <c r="E169" t="s">
-        <v>422</v>
-      </c>
-      <c r="F169" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8">
-      <c r="C170" t="s">
-        <v>424</v>
-      </c>
-      <c r="F170" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8">
-      <c r="C171" t="s">
-        <v>426</v>
-      </c>
-      <c r="F171" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8">
-      <c r="B172" t="s">
-        <v>428</v>
-      </c>
-      <c r="E172" t="s">
-        <v>429</v>
-      </c>
-      <c r="F172" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8">
-      <c r="C173" t="s">
-        <v>431</v>
-      </c>
-      <c r="E173" t="s">
-        <v>432</v>
-      </c>
-      <c r="F173" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8">
-      <c r="B174" t="s">
-        <v>434</v>
-      </c>
-      <c r="E174" t="s">
-        <v>435</v>
-      </c>
-      <c r="F174" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8">
-      <c r="C175" t="s">
-        <v>437</v>
-      </c>
-      <c r="E175" t="s">
-        <v>438</v>
-      </c>
-      <c r="F175" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8">
-      <c r="C176" t="s">
-        <v>440</v>
-      </c>
-      <c r="E176" t="s">
-        <v>441</v>
-      </c>
-      <c r="F176" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8">
-      <c r="C177" t="s">
-        <v>443</v>
-      </c>
-      <c r="F177" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8">
-      <c r="C178" t="s">
-        <v>445</v>
-      </c>
-      <c r="F178" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8">
-      <c r="C179" t="s">
-        <v>447</v>
-      </c>
-      <c r="F179" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8">
-      <c r="B180" t="s">
-        <v>449</v>
-      </c>
-      <c r="E180" t="s">
-        <v>450</v>
-      </c>
-      <c r="F180" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8">
-      <c r="B181" t="s">
-        <v>452</v>
-      </c>
-      <c r="E181" t="s">
-        <v>453</v>
-      </c>
-      <c r="F181" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8">
-      <c r="C182" t="s">
-        <v>455</v>
-      </c>
-      <c r="E182" t="s">
-        <v>456</v>
-      </c>
-      <c r="F182" t="s">
-        <v>457</v>
       </c>
     </row>
   </sheetData>
